--- a/documents/Etat_Rapprochement_Orabank.xlsx
+++ b/documents/Etat_Rapprochement_Orabank.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RELEVE_NON_POINTEE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="JOURNAL_NON_POINTEE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="RAPPROCHEMENT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RELEVE_NON_POINTEE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JOURNAL_NON_POINTEE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPPROCHEMENT" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,9 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -59,13 +57,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -450,13 +446,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>N° d'ordre</t>
+          <t>n° d'ordre</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -491,12 +487,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -513,25 +509,25 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RETRAIT ESPECES CPT 6000760 Ret cheq N 6000760 du 06/10/2025 Porteur : BADAKI ABLO MNI-B 91332293</t>
+          <t>ESPECES CPT 5689526 N 5689526 : ABALO PADANAM 90156097</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249000</v>
+        <v>499550</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -539,184 +535,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RETRAIT ESPECES CPT 6000767 Ret cheq N 6000767 du 13/10/2025 Porteur : BAWILISSIM DONSOSSOU 90021198</t>
+          <t>CHEQUES AUTRE BANQUE - UTB SOKODE SOKODE</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>541000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RETRAIT ESPECES CPT 6000657 Ret cheq N 6000657 du 11/11/2025 Porteur : BLEWOU COMLAN YOM</t>
+          <t>CHEQUES AUTRE BANQUE - ECOBANK VICTOIRE VICTOIRE</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>280000</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>45</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>20/11/2025</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>20/11/2025</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000782 Ret cheq N 6000782</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>322500</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>21/11/2025</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21/11/2025</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000798 Ret cheq N 6000798 du 21/11/2025 Porteur : N'BOUKE ESSI DELALI 90 97 97 27</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>352500</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>48</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>21/11/2025</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>21/11/2025</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VERSEMENT ESPECE CPT COURANT Versement especes Bord N 909502 ATTIGLOH KOFFI MAWULI 93174711</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>52</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>24/11/2025</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>24/11/2025</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000664 Ret cheq N 6000664 du 24/11/2025 Porteur : SEDJRO AFANTOLOU 93237688</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>153000</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>56</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>27/11/2025</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>27/11/2025</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000792 Ret cheq N 6000792 du 27/11/2025 Porteur : KOUDJANE TAFAN97187002</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>388000</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
+        <v>316500</v>
       </c>
     </row>
   </sheetData>
@@ -764,12 +630,14 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>45931</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Solde au 01/10/2025</t>
+          <t>Solde au  31/10/2025</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -781,110 +649,125 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>45936</v>
+        <v>17</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Retrait en especes chq n° 6000760</t>
+          <t xml:space="preserve">Remise de chèque à l'encaissement n° </t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="E3" t="n">
-        <v>2149000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="3" t="n">
-        <v>45943</v>
+      <c r="A4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Retrait en especes chq n° 6000767</t>
+          <t>Cheque n° 5810881    MD25-1129</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>451000</v>
+        <v>1264500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>45972</v>
+        <v>24</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Retrait en especes chq n° 6000657</t>
+          <t>Cheque n° 5810883    OP25-0238</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>820000</v>
+        <v>1177000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>45979</v>
+        <v>37</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Retrait en especes chq n° 6000783</t>
+          <t>Cheque n° 5810886   MD25-1269-1270</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>232500</v>
+        <v>249924</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>45982</v>
+        <v>76</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Retrait en especes chq n° 6000798</t>
+          <t>Cheque n° 5810908   MD25-1278</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>532500</v>
+        <v>4281461</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>45982</v>
+        <v>78</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Versement especes bve 909502</t>
+          <t xml:space="preserve">Remise de chèque à l'encaissement n° </t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9100</v>
+        <v>200700</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -892,40 +775,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>41</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>45985</v>
+        <v>88</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Retrait en especes chq n° 6000664</t>
+          <t>Versement en especes n°  BV n°  j/11/2025,</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>906900</v>
       </c>
       <c r="E9" t="n">
-        <v>513000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>45</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>45988</v>
+        <v>92</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Retrait en especes chq n° 6000792</t>
+          <t>Versement en especes n°  BV n°  j/11/2025,</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="E10" t="n">
-        <v>838000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -939,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -951,462 +838,336 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Libellés</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Compte courant</t>
         </is>
       </c>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Relevé bancaire</t>
         </is>
       </c>
-      <c r="F1" s="4" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Débit</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Crédit</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Débit</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Crédit</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Solde à rectifier</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
-        <v>-877503</v>
-      </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n">
-        <v>1365297</v>
+      <c r="C3" s="5" t="n">
+        <v>313751438</v>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n">
+        <v>319349673</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>30/09/2025</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Chq n° 59996</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n">
-        <v>2580000</v>
-      </c>
-      <c r="F4" s="7" t="n"/>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remise de chèque à l'encaissement n° </t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n">
+        <v>27000</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>30/09/2025</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Encaissement de chq CCT </t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Cheque n° 5810881    MD25-1129</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n">
+        <v>1264500</v>
+      </c>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cheque n° 5810883    OP25-0238</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n">
+        <v>1177000</v>
+      </c>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Cheque n° 5810886   MD25-1269-1270</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n">
+        <v>249924</v>
+      </c>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ESPECES CPT 5689526 N 5689526 : ABALO PADANAM 90156097</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n">
+        <v>499550</v>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>CHEQUES AUTRE BANQUE - UTB SOKODE SOKODE</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
         <v>58000</v>
       </c>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>06/10/2025</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Retrait en especes chq n° 6000760</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>2149000</v>
-      </c>
-      <c r="F6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>06/10/2025</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000760 Ret cheq N 6000760 du 06/10/2025 Porteur : BADAKI ABLO MNI-B 91332293</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n">
-        <v>1249000</v>
-      </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>13/10/2025</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Retrait en especes chq n° 6000767</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n">
-        <v>451000</v>
-      </c>
-      <c r="F8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>13/10/2025</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000767 Ret cheq N 6000767 du 13/10/2025 Porteur : BAWILISSIM DONSOSSOU 90021198</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n">
-        <v>541000</v>
-      </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>11/11/2025</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Retrait en especes chq n° 6000657</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n">
-        <v>820000</v>
-      </c>
-      <c r="F10" s="7" t="n"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Cheque n° 5810908   MD25-1278</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n">
+        <v>4281461</v>
+      </c>
+      <c r="F10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>11/11/2025</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000657 Ret cheq N 6000657 du 11/11/2025 Porteur : BLEWOU COMLAN YOM</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n">
-        <v>280000</v>
-      </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remise de chèque à l'encaissement n° </t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n">
+        <v>200700</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>18/11/2025</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Retrait en especes chq n° 6000783</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n">
-        <v>232500</v>
-      </c>
-      <c r="F12" s="7" t="n"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CHEQUES AUTRE BANQUE - ECOBANK VICTOIRE VICTOIRE</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>316500</v>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>20/11/2025</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000782 Ret cheq N 6000782</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n">
-        <v>322500</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Versement en especes n°  BV n°  j/11/2025,</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n">
+        <v>906900</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>21/11/2025</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Retrait en especes chq n° 6000798</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n">
-        <v>532500</v>
-      </c>
-      <c r="F14" s="7" t="n"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Versement en especes n°  BV n°  j/11/2025,</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n">
+        <v>115000</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>21/11/2025</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Versement especes bve 909502</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n">
-        <v>9100</v>
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Totaux</t>
+        </is>
+      </c>
+      <c r="C15" s="8">
+        <f>SUM(C3:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="8">
+        <f>SUM(D3:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="8">
+        <f>SUM(E3:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="8">
+        <f>SUM(F3:F14)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>21/11/2025</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000798 Ret cheq N 6000798 du 21/11/2025 Porteur : N'BOUKE ESSI DELALI 90 97 97 27</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n">
-        <v>352500</v>
-      </c>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Solde rectifié au 25/12/2025</t>
+        </is>
+      </c>
+      <c r="C16" s="8">
+        <f>IF(D15-C15&gt;0, D15-C15, "")</f>
+        <v/>
+      </c>
+      <c r="D16" s="8">
+        <f>IF(C15-D15&gt;0, C15-D15, "")</f>
+        <v/>
+      </c>
+      <c r="E16" s="8">
+        <f>IF(F15-E15&gt;0, F15-E15, "")</f>
+        <v/>
+      </c>
+      <c r="F16" s="8">
+        <f>IF(E15-F15&gt;0, E15-F15, "")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>21/11/2025</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>VERSEMENT ESPECE CPT COURANT Versement especes Bord N 909502 ATTIGLOH KOFFI MAWULI 93174711</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>1900</v>
-      </c>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>24/11/2025</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Retrait en especes chq n° 6000664</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n">
-        <v>513000</v>
-      </c>
-      <c r="F18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>24/11/2025</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000664 Ret cheq N 6000664 du 24/11/2025 Porteur : SEDJRO AFANTOLOU 93237688</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n">
-        <v>153000</v>
-      </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>27/11/2025</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Retrait en especes chq n° 6000792</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n">
-        <v>838000</v>
-      </c>
-      <c r="F20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>27/11/2025</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>RETRAIT ESPECES CPT 6000792 Ret cheq N 6000792 du 27/11/2025 Porteur : KOUDJANE TAFAN97187002</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n">
-        <v>388000</v>
-      </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n"/>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Totaux</t>
-        </is>
-      </c>
-      <c r="C22" s="10">
-        <f>SUM(C3:C21)</f>
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>TOTAUX GENERAUX</t>
+        </is>
+      </c>
+      <c r="C17" s="8">
+        <f>SUM(C15, C16)</f>
         <v/>
       </c>
-      <c r="D22" s="10">
-        <f>SUM(D3:D21)</f>
+      <c r="D17" s="8">
+        <f>SUM(D15, D16)</f>
         <v/>
       </c>
-      <c r="E22" s="10">
-        <f>SUM(E3:E21)</f>
+      <c r="E17" s="8">
+        <f>SUM(E15, E16)</f>
         <v/>
       </c>
-      <c r="F22" s="10">
-        <f>SUM(F3:F21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Solde rectifié au 30/11/2025</t>
-        </is>
-      </c>
-      <c r="C23" s="10">
-        <f>IF(D22-C22&gt;0, D22-C22, "")</f>
-        <v/>
-      </c>
-      <c r="D23" s="10">
-        <f>IF(C22-D22&gt;0, C22-D22, "")</f>
-        <v/>
-      </c>
-      <c r="E23" s="10">
-        <f>IF(F22-E22&gt;0, F22-E22, "")</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
-        <f>IF(E22-F22&gt;0, E22-F22, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>TOTAUX GENERAUX</t>
-        </is>
-      </c>
-      <c r="C24" s="10">
-        <f>SUM(C22, C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="10">
-        <f>SUM(D22, D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="10">
-        <f>SUM(E22, E23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="10">
-        <f>SUM(F22, F23)</f>
+      <c r="F17" s="8">
+        <f>SUM(F15, F16)</f>
         <v/>
       </c>
     </row>
